--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_终局（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="497">
   <si>
     <t>ID</t>
   </si>
@@ -345,6 +345,9 @@
     <t>来做个交易吧，亚当。选择让我活下来，我便会大方地将你，还有梅森过去的被纳丁达克夺走的记忆完完整整地交还给你们。</t>
   </si>
   <si>
+    <t>7 enhanced litesaturation-horror</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Abaddon; 层级=26</t>
   </si>
   <si>
@@ -502,6 +505,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -897,10 +905,16 @@
     <t>空气在这一刻变得黏稠而沉重，仿佛有无数看不见的虫子在周围的墙壁里蠕动，让呼吸都成为了一种代价高昂的奢求。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>98</t>
   </si>
   <si>
     <t>为什么要告诉我们这一切？</t>
+  </si>
+  <si>
+    <t>19 enhanced_suspense-tension-background-music</t>
   </si>
   <si>
     <t>源类型=type:txt_You; 层级=25</t>
@@ -3791,7 +3805,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" ht="40.5" spans="1:12">
+    <row r="28" ht="45" spans="1:12">
       <c r="A28" t="s">
         <v>101</v>
       </c>
@@ -3817,7 +3831,7 @@
         <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
@@ -3826,12 +3840,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" ht="54" spans="1:12">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
         <v>28</v>
@@ -3849,7 +3863,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3864,15 +3878,15 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" ht="30" spans="1:12">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -3887,7 +3901,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3902,12 +3916,12 @@
         <v>35</v>
       </c>
       <c r="L30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" ht="58.5" spans="1:12">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3925,7 +3939,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3940,12 +3954,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" ht="54" spans="1:12">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3963,7 +3977,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3978,12 +3992,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" ht="54" spans="1:12">
       <c r="A33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4001,7 +4015,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4016,12 +4030,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" ht="57" spans="1:12">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4039,7 +4053,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4054,21 +4068,21 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" ht="55.5" spans="1:12">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -4077,7 +4091,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4092,12 +4106,12 @@
         <v>31</v>
       </c>
       <c r="L35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:12">
       <c r="A36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
         <v>53</v>
@@ -4106,7 +4120,7 @@
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4115,7 +4129,7 @@
         <v>54</v>
       </c>
       <c r="G36" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4130,12 +4144,12 @@
         <v>83</v>
       </c>
       <c r="L36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:12">
       <c r="A37" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B37" t="s">
         <v>53</v>
@@ -4153,7 +4167,7 @@
         <v>54</v>
       </c>
       <c r="G37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4168,12 +4182,12 @@
         <v>87</v>
       </c>
       <c r="L37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" ht="42" spans="1:12">
       <c r="A38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4188,7 +4202,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4203,12 +4217,12 @@
         <v>35</v>
       </c>
       <c r="L38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" ht="42" spans="1:12">
       <c r="A39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
@@ -4223,7 +4237,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4238,15 +4252,15 @@
         <v>31</v>
       </c>
       <c r="L39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" ht="30" spans="1:12">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
@@ -4258,10 +4272,10 @@
         <v>15</v>
       </c>
       <c r="F40" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4276,12 +4290,12 @@
         <v>83</v>
       </c>
       <c r="L40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" ht="40.5" spans="1:12">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B41" t="s">
         <v>28</v>
@@ -4296,10 +4310,10 @@
         <v>15</v>
       </c>
       <c r="F41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4311,15 +4325,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" ht="42" spans="1:12">
       <c r="A42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4337,7 +4351,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4352,12 +4366,12 @@
         <v>35</v>
       </c>
       <c r="L42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" ht="40.5" spans="1:12">
       <c r="A43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4375,7 +4389,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4390,12 +4404,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" ht="40.5" spans="1:12">
       <c r="A44" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4413,7 +4427,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4425,15 +4439,15 @@
         <v>15</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" ht="42" spans="1:12">
       <c r="A45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4451,7 +4465,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4471,7 +4485,7 @@
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4489,7 +4503,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4509,7 +4523,7 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4527,7 +4541,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4547,7 +4561,7 @@
     </row>
     <row r="48" ht="69" spans="1:12">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4565,7 +4579,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4580,12 +4594,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" ht="30" spans="1:12">
       <c r="A49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4603,7 +4617,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4623,7 +4637,7 @@
     </row>
     <row r="50" ht="57" spans="1:12">
       <c r="A50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4641,7 +4655,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4661,7 +4675,7 @@
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4679,7 +4693,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4694,12 +4708,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4717,7 +4731,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4732,12 +4746,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" ht="55.5" spans="1:12">
       <c r="A53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B53" t="s">
         <v>28</v>
@@ -4755,7 +4769,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4770,12 +4784,12 @@
         <v>31</v>
       </c>
       <c r="L53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" ht="54" spans="1:12">
       <c r="A54" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4793,7 +4807,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4813,16 +4827,16 @@
     </row>
     <row r="55" ht="30" spans="1:12">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4831,7 +4845,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4846,12 +4860,12 @@
         <v>31</v>
       </c>
       <c r="L55" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" ht="43.5" spans="1:12">
       <c r="A56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4860,7 +4874,7 @@
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -4869,7 +4883,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4884,21 +4898,21 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" ht="42" spans="1:12">
       <c r="A57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4907,7 +4921,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4922,12 +4936,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" ht="30" spans="1:12">
       <c r="A58" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B58" t="s">
         <v>28</v>
@@ -4936,7 +4950,7 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -4945,7 +4959,7 @@
         <v>29</v>
       </c>
       <c r="G58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4965,7 +4979,7 @@
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4983,7 +4997,7 @@
         <v>29</v>
       </c>
       <c r="G59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4998,12 +5012,12 @@
         <v>87</v>
       </c>
       <c r="L59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="60" ht="43.5" spans="1:12">
       <c r="A60" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B60" t="s">
         <v>28</v>
@@ -5021,7 +5035,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5036,12 +5050,12 @@
         <v>31</v>
       </c>
       <c r="L60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="61" ht="43.5" spans="1:12">
       <c r="A61" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B61" t="s">
         <v>28</v>
@@ -5059,7 +5073,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5074,12 +5088,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" ht="42" spans="1:12">
       <c r="A62" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5097,7 +5111,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5117,7 +5131,7 @@
     </row>
     <row r="63" ht="45" spans="1:12">
       <c r="A63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B63" t="s">
         <v>28</v>
@@ -5135,7 +5149,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5150,12 +5164,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" ht="57" spans="1:12">
       <c r="A64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B64" t="s">
         <v>28</v>
@@ -5173,7 +5187,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5193,7 +5207,7 @@
     </row>
     <row r="65" ht="30" spans="1:12">
       <c r="A65" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5211,7 +5225,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5231,7 +5245,7 @@
     </row>
     <row r="66" ht="54" spans="1:12">
       <c r="A66" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B66" t="s">
         <v>28</v>
@@ -5249,7 +5263,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5264,12 +5278,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67" ht="40.5" spans="1:12">
       <c r="A67" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5287,7 +5301,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5307,7 +5321,7 @@
     </row>
     <row r="68" ht="27" spans="1:12">
       <c r="A68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5325,7 +5339,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5340,12 +5354,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="69" ht="40.5" spans="1:12">
       <c r="A69" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5363,7 +5377,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5375,24 +5389,24 @@
         <v>15</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B70" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
@@ -5401,7 +5415,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5416,12 +5430,12 @@
         <v>31</v>
       </c>
       <c r="L70" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" ht="27" spans="1:12">
       <c r="A71" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5430,7 +5444,7 @@
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -5439,7 +5453,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5459,7 +5473,7 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5477,7 +5491,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5497,7 +5511,7 @@
     </row>
     <row r="73" ht="27" spans="1:12">
       <c r="A73" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5515,7 +5529,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5530,12 +5544,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B74" t="s">
         <v>28</v>
@@ -5553,7 +5567,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5568,12 +5582,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="75" ht="27" spans="1:12">
       <c r="A75" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5591,7 +5605,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5603,7 +5617,7 @@
         <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L75" t="s">
         <v>39</v>
@@ -5611,7 +5625,7 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B76" t="s">
         <v>28</v>
@@ -5629,7 +5643,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5649,7 +5663,7 @@
     </row>
     <row r="77" ht="42" spans="1:12">
       <c r="A77" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B77" t="s">
         <v>28</v>
@@ -5667,7 +5681,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5687,7 +5701,7 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5705,7 +5719,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5717,7 +5731,7 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L78" t="s">
         <v>48</v>
@@ -5725,7 +5739,7 @@
     </row>
     <row r="79" ht="43.5" spans="1:12">
       <c r="A79" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B79" t="s">
         <v>28</v>
@@ -5743,7 +5757,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5758,12 +5772,12 @@
         <v>31</v>
       </c>
       <c r="L79" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="80" ht="30" spans="1:12">
       <c r="A80" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B80" t="s">
         <v>28</v>
@@ -5781,7 +5795,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5796,12 +5810,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="81" ht="54" spans="1:12">
       <c r="A81" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B81" t="s">
         <v>28</v>
@@ -5819,7 +5833,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5834,12 +5848,12 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" ht="58.5" spans="1:12">
       <c r="A82" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B82" t="s">
         <v>28</v>
@@ -5857,7 +5871,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5872,12 +5886,12 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="83" ht="42" spans="1:12">
       <c r="A83" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B83" t="s">
         <v>28</v>
@@ -5895,7 +5909,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5915,7 +5929,7 @@
     </row>
     <row r="84" ht="30" spans="1:12">
       <c r="A84" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5933,7 +5947,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5945,15 +5959,15 @@
         <v>15</v>
       </c>
       <c r="K84" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L84" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85" ht="70.5" spans="1:12">
       <c r="A85" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B85" t="s">
         <v>28</v>
@@ -5971,7 +5985,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -5986,12 +6000,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="86" ht="55.5" spans="1:12">
       <c r="A86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6009,7 +6023,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6029,7 +6043,7 @@
     </row>
     <row r="87" ht="40.5" spans="1:12">
       <c r="A87" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6047,7 +6061,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6067,7 +6081,7 @@
     </row>
     <row r="88" ht="69" spans="1:12">
       <c r="A88" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B88" t="s">
         <v>28</v>
@@ -6085,7 +6099,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6100,12 +6114,12 @@
         <v>31</v>
       </c>
       <c r="L88" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="89" ht="30" spans="1:12">
       <c r="A89" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6123,7 +6137,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6138,12 +6152,12 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" ht="43.5" spans="1:12">
       <c r="A90" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B90" t="s">
         <v>28</v>
@@ -6161,7 +6175,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6176,12 +6190,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="91" ht="30" spans="1:12">
       <c r="A91" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B91" t="s">
         <v>28</v>
@@ -6199,7 +6213,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6214,12 +6228,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="92" ht="30" spans="1:12">
       <c r="A92" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6237,7 +6251,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6252,12 +6266,12 @@
         <v>35</v>
       </c>
       <c r="L92" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="93" ht="40.5" spans="1:12">
       <c r="A93" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6272,27 +6286,27 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
       </c>
       <c r="I93" t="s">
-        <v>15</v>
+        <v>282</v>
       </c>
       <c r="J93" t="s">
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" ht="60" spans="1:12">
       <c r="A94" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B94" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
@@ -6307,13 +6321,13 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
       </c>
       <c r="I94" t="s">
-        <v>15</v>
+        <v>285</v>
       </c>
       <c r="J94" t="s">
         <v>15</v>
@@ -6322,12 +6336,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="95" ht="40.5" spans="1:12">
       <c r="A95" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6345,7 +6359,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6360,15 +6374,15 @@
         <v>15</v>
       </c>
       <c r="L95" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="96" ht="40.5" spans="1:12">
       <c r="A96" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
@@ -6383,7 +6397,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6398,12 +6412,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="97" ht="40.5" spans="1:12">
       <c r="A97" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6421,7 +6435,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6436,12 +6450,12 @@
         <v>15</v>
       </c>
       <c r="L97" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="98" ht="40.5" spans="1:12">
       <c r="A98" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B98" t="s">
         <v>28</v>
@@ -6459,7 +6473,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6474,12 +6488,12 @@
         <v>31</v>
       </c>
       <c r="L98" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="99" ht="40.5" spans="1:12">
       <c r="A99" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6497,7 +6511,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6512,12 +6526,12 @@
         <v>15</v>
       </c>
       <c r="L99" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="100" ht="30" spans="1:12">
       <c r="A100" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B100" t="s">
         <v>28</v>
@@ -6535,7 +6549,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6550,12 +6564,12 @@
         <v>15</v>
       </c>
       <c r="L100" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="101" ht="30" spans="1:12">
       <c r="A101" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B101" t="s">
         <v>28</v>
@@ -6573,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="G101" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H101" t="s">
         <v>15</v>
@@ -6588,12 +6602,12 @@
         <v>15</v>
       </c>
       <c r="L101" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="102" ht="40.5" spans="1:12">
       <c r="A102" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B102" t="s">
         <v>13</v>
@@ -6611,7 +6625,7 @@
         <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H102" t="s">
         <v>15</v>
@@ -6626,12 +6640,12 @@
         <v>15</v>
       </c>
       <c r="L102" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="103" ht="55.5" spans="1:12">
       <c r="A103" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B103" t="s">
         <v>28</v>
@@ -6649,7 +6663,7 @@
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H103" t="s">
         <v>15</v>
@@ -6664,12 +6678,12 @@
         <v>15</v>
       </c>
       <c r="L103" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="104" ht="40.5" spans="1:12">
       <c r="A104" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
@@ -6687,7 +6701,7 @@
         <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="H104" t="s">
         <v>15</v>
@@ -6702,12 +6716,12 @@
         <v>15</v>
       </c>
       <c r="L104" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="105" ht="67.5" spans="1:12">
       <c r="A105" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B105" t="s">
         <v>28</v>
@@ -6725,7 +6739,7 @@
         <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H105" t="s">
         <v>15</v>
@@ -6737,10 +6751,10 @@
         <v>15</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L105" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -6761,55 +6775,55 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B5" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -6817,66 +6831,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B10" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B11" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B12" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B13" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B15" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -6898,616 +6912,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E4" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B5" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D5" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E5" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B6" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D6" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F6" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B7" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C7" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E7" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F7" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B8" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C8" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D8" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E8" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F8" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B9" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C9" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D9" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E9" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F9" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B10" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C10" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D10" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E10" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F10" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C11" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D11" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E11" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F11" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B12" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C12" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D12" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E12" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F12" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B13" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C13" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D13" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E13" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F13" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B14" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C14" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D14" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E14" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F14" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B15" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C15" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D15" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E15" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F15" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B16" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C16" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D16" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E16" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F16" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B17" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C17" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D17" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E17" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F17" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B18" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C18" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D18" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E18" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F18" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B19" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C19" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D19" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E19" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F19" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B20" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C20" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D20" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E20" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F20" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B21" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C21" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D21" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E21" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F21" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B22" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C22" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D22" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E22" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F22" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B23" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C23" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D23" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E23" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F23" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B24" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C24" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D24" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E24" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F24" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B25" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C25" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D25" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E25" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F25" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B26" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C26" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D26" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E26" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F26" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B27" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C27" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D27" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E27" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F27" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B28" t="s">
+        <v>479</v>
+      </c>
+      <c r="C28" t="s">
+        <v>480</v>
+      </c>
+      <c r="D28" t="s">
         <v>476</v>
       </c>
-      <c r="C28" t="s">
-        <v>477</v>
-      </c>
-      <c r="D28" t="s">
-        <v>473</v>
-      </c>
       <c r="E28" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F28" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B29" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C29" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D29" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E29" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="F29" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B30" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C30" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D30" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E30" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F30" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B31" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C31" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D31" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_终局（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="498">
   <si>
     <t>ID</t>
   </si>
@@ -915,6 +915,9 @@
   </si>
   <si>
     <t>19 enhanced_suspense-tension-background-music</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music19)</t>
   </si>
   <si>
     <t>源类型=type:txt_You; 层级=25</t>
@@ -6333,15 +6336,15 @@
         <v>15</v>
       </c>
       <c r="K94" t="s">
-        <v>15</v>
+        <v>286</v>
       </c>
       <c r="L94" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="95" ht="40.5" spans="1:12">
       <c r="A95" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6359,7 +6362,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6374,12 +6377,12 @@
         <v>15</v>
       </c>
       <c r="L95" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="96" ht="40.5" spans="1:12">
       <c r="A96" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B96" t="s">
         <v>109</v>
@@ -6397,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6412,12 +6415,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="97" ht="40.5" spans="1:12">
       <c r="A97" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6435,7 +6438,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6450,12 +6453,12 @@
         <v>15</v>
       </c>
       <c r="L97" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="98" ht="40.5" spans="1:12">
       <c r="A98" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B98" t="s">
         <v>28</v>
@@ -6473,7 +6476,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6488,12 +6491,12 @@
         <v>31</v>
       </c>
       <c r="L98" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="99" ht="40.5" spans="1:12">
       <c r="A99" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6511,7 +6514,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6531,7 +6534,7 @@
     </row>
     <row r="100" ht="30" spans="1:12">
       <c r="A100" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B100" t="s">
         <v>28</v>
@@ -6549,7 +6552,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6564,12 +6567,12 @@
         <v>15</v>
       </c>
       <c r="L100" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="101" ht="30" spans="1:12">
       <c r="A101" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B101" t="s">
         <v>28</v>
@@ -6587,7 +6590,7 @@
         <v>15</v>
       </c>
       <c r="G101" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H101" t="s">
         <v>15</v>
@@ -6602,12 +6605,12 @@
         <v>15</v>
       </c>
       <c r="L101" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="102" ht="40.5" spans="1:12">
       <c r="A102" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B102" t="s">
         <v>13</v>
@@ -6625,7 +6628,7 @@
         <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H102" t="s">
         <v>15</v>
@@ -6640,12 +6643,12 @@
         <v>15</v>
       </c>
       <c r="L102" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="103" ht="55.5" spans="1:12">
       <c r="A103" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B103" t="s">
         <v>28</v>
@@ -6663,7 +6666,7 @@
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H103" t="s">
         <v>15</v>
@@ -6678,12 +6681,12 @@
         <v>15</v>
       </c>
       <c r="L103" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="104" ht="40.5" spans="1:12">
       <c r="A104" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
@@ -6701,7 +6704,7 @@
         <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H104" t="s">
         <v>15</v>
@@ -6716,12 +6719,12 @@
         <v>15</v>
       </c>
       <c r="L104" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="105" ht="67.5" spans="1:12">
       <c r="A105" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B105" t="s">
         <v>28</v>
@@ -6739,7 +6742,7 @@
         <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H105" t="s">
         <v>15</v>
@@ -6751,10 +6754,10 @@
         <v>15</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L105" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -6775,47 +6778,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B6" t="s">
         <v>158</v>
@@ -6823,7 +6826,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -6831,7 +6834,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B8" t="s">
         <v>218</v>
@@ -6839,7 +6842,7 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B9" t="s">
         <v>203</v>
@@ -6847,50 +6850,50 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B13" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -6912,616 +6915,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B12" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C12" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B15" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B16" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C16" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E16" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F16" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E17" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F17" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B18" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C18" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D18" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E18" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F18" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B19" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C19" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E19" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B20" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D20" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E20" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F20" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B21" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C21" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D21" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E21" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F21" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B22" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C22" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D22" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E22" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F22" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B23" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C24" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D24" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E24" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F24" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B25" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C25" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D25" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E25" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F25" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B26" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C26" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D26" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E26" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F26" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B27" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C27" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D27" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E27" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F27" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B28" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C28" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D28" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E28" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F28" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B29" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C29" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D29" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E29" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F29" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B30" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C30" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F30" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B31" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C31" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D31" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
